--- a/data/raw/sales/Week 27/Audio_Array/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 27/Audio_Array/Seller Sales (SP-API).xlsx
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>8522.879999999999</v>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
-        <v>58197.46</v>
+        <v>53794.07</v>
       </c>
       <c r="H42" t="n">
         <v>3041</v>
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>28810.17</v>
+        <v>21607.63</v>
       </c>
       <c r="H117" t="n">
         <v>426</v>
